--- a/modules/acne/backend/templates/acne_packing_template_kr.xlsx
+++ b/modules/acne/backend/templates/acne_packing_template_kr.xlsx
@@ -329,10 +329,10 @@
     </r>
   </si>
   <si>
-    <t>Gyeonggi-do 17405</t>
+    <t>Gyeonggi-do 12646</t>
   </si>
   <si>
-    <t>Dock 1, 2F, 1911, Hwangmu-ro, Bubal-eup, Icheon-si</t>
+    <t>Dock 12, 2F, 536, Yeojunam-ro, Ganam-eup, Yeoju-si</t>
   </si>
   <si>
     <t>Acne Studios Korea LLC</t>
@@ -356,7 +356,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Maersk Logistics DC8 </t>
+      <t xml:space="preserve">Maersk Logistics DC11 </t>
     </r>
   </si>
   <si>
